--- a/Sindhi Muslim/Salary Sheet/Salary Sheet - October-2024.xlsx
+++ b/Sindhi Muslim/Salary Sheet/Salary Sheet - October-2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Salary Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C359049-2CF1-4B6E-983C-86DEA53C88A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3274181E-D2B8-40E1-8A77-FA2563B8103C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attandance" sheetId="3" r:id="rId1"/>
@@ -334,7 +334,7 @@
     <t>41105-4725771-0</t>
   </si>
   <si>
-    <t>0010108832370019</t>
+    <t>0003936299331000</t>
   </si>
 </sst>
 </file>
@@ -925,6 +925,60 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -934,14 +988,8 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -961,15 +1009,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -979,9 +1018,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -999,42 +1035,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3828,6 +3828,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3848,56 +3851,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="73" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="57"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="75"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="80" t="s">
+      <c r="C3" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="80" t="s">
+      <c r="D3" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="E3" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="67" t="s">
+      <c r="F3" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="67" t="s">
+      <c r="G3" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="67" t="s">
+      <c r="H3" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="73" t="s">
+      <c r="I3" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="87" t="s">
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="66" t="s">
         <v>77</v>
       </c>
       <c r="N3" s="58" t="s">
@@ -3905,43 +3908,43 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="78"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="83" t="s">
+      <c r="A4" s="90"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="90" t="s">
+      <c r="J4" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="85" t="s">
+      <c r="K4" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="85" t="s">
+      <c r="L4" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="88"/>
+      <c r="M4" s="67"/>
       <c r="N4" s="59"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="79"/>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="91"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="89"/>
+      <c r="A5" s="91"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="68"/>
       <c r="N5" s="60"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -4358,56 +4361,56 @@
     </row>
     <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:14" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="73" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="56"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="57"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="74"/>
+      <c r="K16" s="74"/>
+      <c r="L16" s="74"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="77" t="s">
+      <c r="A18" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="80" t="s">
+      <c r="B18" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="80" t="s">
+      <c r="C18" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="80" t="s">
+      <c r="D18" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="67" t="s">
+      <c r="E18" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="67" t="s">
+      <c r="F18" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="G18" s="70" t="s">
+      <c r="G18" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="H18" s="70" t="s">
+      <c r="H18" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="I18" s="73" t="s">
+      <c r="I18" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="J18" s="73"/>
-      <c r="K18" s="73"/>
-      <c r="L18" s="73"/>
-      <c r="M18" s="74" t="s">
+      <c r="J18" s="63"/>
+      <c r="K18" s="63"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="86" t="s">
         <v>77</v>
       </c>
       <c r="N18" s="58" t="s">
@@ -4415,43 +4418,43 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="78"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="61" t="s">
+      <c r="A19" s="90"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="63" t="s">
+      <c r="J19" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="K19" s="65" t="s">
+      <c r="K19" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="L19" s="65" t="s">
+      <c r="L19" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="M19" s="75"/>
+      <c r="M19" s="87"/>
       <c r="N19" s="59"/>
     </row>
     <row r="20" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="79"/>
-      <c r="B20" s="69"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="69"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="66"/>
-      <c r="M20" s="76"/>
+      <c r="A20" s="91"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="80"/>
+      <c r="K20" s="82"/>
+      <c r="L20" s="82"/>
+      <c r="M20" s="88"/>
       <c r="N20" s="60"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -4474,7 +4477,7 @@
         <v>83</v>
       </c>
       <c r="G21" s="47" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H21" s="48">
         <v>60000</v>
@@ -4519,8 +4522,8 @@
       <c r="F22" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="G22" s="18" t="s">
-        <v>70</v>
+      <c r="G22" s="28" t="s">
+        <v>75</v>
       </c>
       <c r="H22" s="19">
         <v>24000</v>
@@ -4565,8 +4568,8 @@
       <c r="F23" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="G23" s="18" t="s">
-        <v>71</v>
+      <c r="G23" s="28" t="s">
+        <v>75</v>
       </c>
       <c r="H23" s="19">
         <v>8000</v>
@@ -4611,8 +4614,8 @@
       <c r="F24" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="G24" s="18" t="s">
-        <v>72</v>
+      <c r="G24" s="28" t="s">
+        <v>75</v>
       </c>
       <c r="H24" s="19">
         <v>15000</v>
@@ -4657,8 +4660,8 @@
       <c r="F25" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="G25" s="18" t="s">
-        <v>99</v>
+      <c r="G25" s="28" t="s">
+        <v>75</v>
       </c>
       <c r="H25" s="19">
         <v>15000</v>
@@ -4749,7 +4752,7 @@
         <v>88</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H27" s="25">
         <v>15000</v>
@@ -4777,6 +4780,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="N18:N20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="M18:M20"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="A3:A5"/>
     <mergeCell ref="E18:E20"/>
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="F3:F5"/>
@@ -4793,24 +4812,8 @@
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="N18:N20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="H18:H20"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="M18:M20"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="A3:A5"/>
   </mergeCells>
-  <conditionalFormatting sqref="B6:M6 B7:C10 M7:M13 D7:L14 C11:C13 F21:F27 D22:E26 G22:I26 K22:M27 D27:J27">
+  <conditionalFormatting sqref="B6:M6 B7:C10 M7:M13 D7:L14 C11:C13 F21:F27 D22:E26 K22:M27 D27:J27 G22:I26">
     <cfRule type="expression" dxfId="2" priority="9">
       <formula>$C6=#REF!</formula>
     </cfRule>
@@ -4825,10 +4828,10 @@
       <formula>$C21=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="78" fitToHeight="0" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="N13" formula="1"/>
+    <ignoredError sqref="N13 N24 N26" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Sindhi Muslim/Salary Sheet/Salary Sheet - October-2024.xlsx
+++ b/Sindhi Muslim/Salary Sheet/Salary Sheet - October-2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Salary Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3274181E-D2B8-40E1-8A77-FA2563B8103C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEEC23CF-D500-4547-AD64-E5E3FF454055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="101">
   <si>
     <t>Employee Attendance Sheet</t>
   </si>
@@ -334,7 +334,10 @@
     <t>41105-4725771-0</t>
   </si>
   <si>
-    <t>0003936299331000</t>
+    <t xml:space="preserve">Government High School Sindhi Jamaat Cooperative Housing Society, Bin Qasim Town Karachi </t>
+  </si>
+  <si>
+    <t>Salary Sheet for the Month October 2024</t>
   </si>
 </sst>
 </file>
@@ -347,7 +350,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,8 +420,16 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -467,8 +478,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9CCE4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -641,43 +658,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -781,7 +761,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -820,25 +800,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -847,18 +818,6 @@
     <xf numFmtId="49" fontId="8" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -878,15 +837,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -912,7 +871,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -925,33 +884,54 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -979,61 +959,24 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1407,11 +1350,11 @@
   <sheetData>
     <row r="2" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
       <c r="D3" s="8" t="str">
         <f>TEXT(D4,"ddd")</f>
         <v>Tue</v>
@@ -1536,13 +1479,13 @@
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AI3" s="53" t="s">
+      <c r="AI3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="53"/>
-      <c r="AK3" s="53"/>
-      <c r="AL3" s="53"/>
-      <c r="AM3" s="54"/>
+      <c r="AJ3" s="46"/>
+      <c r="AK3" s="46"/>
+      <c r="AL3" s="46"/>
+      <c r="AM3" s="47"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -1647,19 +1590,19 @@
       <c r="AH4" s="9">
         <v>45596</v>
       </c>
-      <c r="AI4" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ4" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK4" s="41" t="s">
+      <c r="AI4" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ4" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK4" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="AL4" s="41" t="s">
+      <c r="AL4" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="AM4" s="42" t="s">
+      <c r="AM4" s="35" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2483,98 +2426,98 @@
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A12" s="37">
-        <v>8</v>
-      </c>
-      <c r="B12" s="38" t="s">
+      <c r="A12" s="30">
+        <v>8</v>
+      </c>
+      <c r="B12" s="31" t="s">
         <v>91</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="M12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="O12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="S12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="T12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="U12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="V12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="W12" s="39"/>
-      <c r="X12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB12" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC12" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF12" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG12" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH12" s="39" t="s">
+      <c r="D12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="T12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="U12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="V12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="W12" s="32"/>
+      <c r="X12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC12" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD12" s="32"/>
+      <c r="AE12" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF12" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG12" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH12" s="32" t="s">
         <v>6</v>
       </c>
       <c r="AI12" s="10">
@@ -2716,11 +2659,11 @@
     </row>
     <row r="16" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
       <c r="D17" s="8" t="str">
         <f>TEXT(D18,"ddd")</f>
         <v>Tue</v>
@@ -2845,13 +2788,13 @@
         <f t="shared" si="7"/>
         <v>Thu</v>
       </c>
-      <c r="AI17" s="53" t="s">
+      <c r="AI17" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="AJ17" s="53"/>
-      <c r="AK17" s="53"/>
-      <c r="AL17" s="53"/>
-      <c r="AM17" s="54"/>
+      <c r="AJ17" s="46"/>
+      <c r="AK17" s="46"/>
+      <c r="AL17" s="46"/>
+      <c r="AM17" s="47"/>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -2956,19 +2899,19 @@
       <c r="AH18" s="9">
         <v>45596</v>
       </c>
-      <c r="AI18" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ18" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK18" s="41" t="s">
+      <c r="AI18" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ18" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK18" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="AL18" s="41" t="s">
+      <c r="AL18" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="AM18" s="42" t="s">
+      <c r="AM18" s="35" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3558,117 +3501,117 @@
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A24" s="37">
-        <v>6</v>
-      </c>
-      <c r="B24" s="38" t="s">
+      <c r="A24" s="30">
+        <v>6</v>
+      </c>
+      <c r="B24" s="31" t="s">
         <v>96</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="39" t="s">
+      <c r="D24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="E24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="F24" s="39" t="s">
+      <c r="F24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="G24" s="39" t="s">
+      <c r="G24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="H24" s="39" t="s">
+      <c r="H24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39" t="s">
+      <c r="I24" s="32"/>
+      <c r="J24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="K24" s="39" t="s">
+      <c r="K24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="L24" s="39" t="s">
+      <c r="L24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="M24" s="39" t="s">
+      <c r="M24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="N24" s="39" t="s">
+      <c r="N24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="O24" s="39" t="s">
+      <c r="O24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39" t="s">
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="R24" s="39" t="s">
+      <c r="R24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="S24" s="39" t="s">
+      <c r="S24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="T24" s="39" t="s">
+      <c r="T24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="U24" s="39" t="s">
+      <c r="U24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="V24" s="39" t="s">
+      <c r="V24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="W24" s="39"/>
-      <c r="X24" s="39" t="s">
+      <c r="W24" s="32"/>
+      <c r="X24" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="Y24" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z24" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA24" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB24" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC24" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD24" s="39"/>
-      <c r="AE24" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF24" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG24" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH24" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI24" s="39">
+      <c r="Y24" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z24" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA24" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB24" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC24" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD24" s="32"/>
+      <c r="AE24" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF24" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG24" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH24" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI24" s="32">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="AJ24" s="39">
+      <c r="AJ24" s="32">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AK24" s="39">
+      <c r="AK24" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL24" s="39">
+      <c r="AL24" s="32">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="AM24" s="40">
+      <c r="AM24" s="33">
         <f t="shared" si="12"/>
         <v>13</v>
       </c>
@@ -3831,7 +3774,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -3850,247 +3793,188 @@
     <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="73" t="s">
+    <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="75" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="77"/>
+    </row>
+    <row r="2" spans="1:14" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="78" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="80"/>
+    </row>
+    <row r="3" spans="1:14" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="75"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="50"/>
     </row>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="89" t="s">
+    <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B5" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C5" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D5" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="E5" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F5" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="55" t="s">
+      <c r="G5" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="55" t="s">
+      <c r="H5" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="63" t="s">
+      <c r="I5" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="66" t="s">
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="N3" s="58" t="s">
+      <c r="N5" s="51" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="90"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="71" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="69" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" s="64" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" s="64" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4" s="67"/>
-      <c r="N4" s="59"/>
-    </row>
-    <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="91"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="60"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="45">
-        <v>44774</v>
-      </c>
-      <c r="F6" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" s="48">
-        <v>22000</v>
-      </c>
-      <c r="I6" s="44">
-        <v>31</v>
-      </c>
-      <c r="J6" s="44">
-        <f>Attandance!AM5</f>
-        <v>31</v>
-      </c>
-      <c r="K6" s="44">
-        <f>Attandance!AJ5</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="44">
-        <f>Attandance!AK5</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="44"/>
-      <c r="N6" s="49">
-        <f>(H6/31)*J6</f>
-        <v>22000</v>
-      </c>
+      <c r="A6" s="59"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" s="67"/>
+      <c r="N6" s="52"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="29">
-        <v>44774</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" s="30">
-        <v>18000</v>
-      </c>
-      <c r="I7" s="15">
-        <v>31</v>
-      </c>
-      <c r="J7" s="14">
-        <f>Attandance!AM6</f>
-        <v>31</v>
-      </c>
-      <c r="K7" s="14">
-        <f>Attandance!AJ6</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="14">
-        <f>Attandance!AK6</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="15"/>
-      <c r="N7" s="36">
-        <f t="shared" ref="N7:N14" si="0">(H7/31)*J7</f>
-        <v>18000</v>
-      </c>
+    <row r="7" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="60"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="65"/>
+      <c r="L7" s="65"/>
+      <c r="M7" s="68"/>
+      <c r="N7" s="53"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="15" t="s">
+      <c r="A8" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="38">
         <v>44774</v>
       </c>
-      <c r="F8" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8" s="30">
-        <v>15000</v>
-      </c>
-      <c r="I8" s="15">
+      <c r="F8" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="41">
+        <v>22000</v>
+      </c>
+      <c r="I8" s="37">
         <v>31</v>
       </c>
-      <c r="J8" s="14">
-        <f>Attandance!AM7</f>
-        <v>25</v>
-      </c>
-      <c r="K8" s="14">
-        <f>Attandance!AJ7</f>
-        <v>6</v>
-      </c>
-      <c r="L8" s="14">
-        <f>Attandance!AK7</f>
-        <v>1</v>
-      </c>
-      <c r="M8" s="15"/>
-      <c r="N8" s="36">
-        <f>(H8/30)*J8</f>
-        <v>12500</v>
+      <c r="J8" s="37">
+        <v>31</v>
+      </c>
+      <c r="K8" s="37">
+        <v>0</v>
+      </c>
+      <c r="L8" s="37">
+        <v>0</v>
+      </c>
+      <c r="M8" s="37"/>
+      <c r="N8" s="42">
+        <f>(H8/31)*J8</f>
+        <v>22000</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
-        <v>63</v>
+      <c r="A9" s="24" t="s">
+        <v>44</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>11</v>
@@ -4098,44 +3982,42 @@
       <c r="D9" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="29">
-        <v>45198</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="30">
-        <v>15000</v>
+      <c r="E9" s="22">
+        <v>44774</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="23">
+        <v>18000</v>
       </c>
       <c r="I9" s="15">
         <v>31</v>
       </c>
       <c r="J9" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K9" s="14">
-        <f>Attandance!AJ8</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="14">
-        <f>Attandance!AK8</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="15"/>
-      <c r="N9" s="36">
-        <f>(H9/30)*J9</f>
-        <v>14500</v>
+      <c r="N9" s="29">
+        <f t="shared" ref="N9:N16" si="0">(H9/31)*J9</f>
+        <v>18000</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>46</v>
+      <c r="A10" s="24" t="s">
+        <v>45</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>11</v>
@@ -4143,44 +4025,42 @@
       <c r="D10" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="29">
-        <v>45229</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="H10" s="30">
+      <c r="E10" s="22">
+        <v>44774</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" s="23">
         <v>15000</v>
       </c>
       <c r="I10" s="15">
         <v>31</v>
       </c>
       <c r="J10" s="14">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K10" s="14">
-        <f>Attandance!AJ9</f>
+        <v>6</v>
+      </c>
+      <c r="L10" s="14">
         <v>1</v>
       </c>
-      <c r="L10" s="14">
-        <f>Attandance!AK9</f>
-        <v>1</v>
-      </c>
       <c r="M10" s="15"/>
-      <c r="N10" s="36">
+      <c r="N10" s="29">
         <f>(H10/30)*J10</f>
-        <v>14500</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
-        <v>47</v>
+      <c r="A11" s="24" t="s">
+        <v>63</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>11</v>
@@ -4188,650 +4068,705 @@
       <c r="D11" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="29">
-        <v>45323</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" s="30">
-        <v>25000</v>
+      <c r="E11" s="22">
+        <v>45198</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="23">
+        <v>15000</v>
       </c>
       <c r="I11" s="15">
         <v>31</v>
       </c>
       <c r="J11" s="14">
-        <f>Attandance!AM10</f>
+        <v>29</v>
+      </c>
+      <c r="K11" s="14">
+        <v>2</v>
+      </c>
+      <c r="L11" s="14">
+        <v>1</v>
+      </c>
+      <c r="M11" s="15"/>
+      <c r="N11" s="29">
+        <f>(H11/30)*J11</f>
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="22">
+        <v>45229</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" s="23">
+        <v>15000</v>
+      </c>
+      <c r="I12" s="15">
         <v>31</v>
       </c>
-      <c r="K11" s="14">
-        <f>Attandance!AJ10</f>
+      <c r="J12" s="14">
+        <v>29</v>
+      </c>
+      <c r="K12" s="14">
+        <v>1</v>
+      </c>
+      <c r="L12" s="14">
+        <v>1</v>
+      </c>
+      <c r="M12" s="15"/>
+      <c r="N12" s="29">
+        <f>(H12/30)*J12</f>
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="22">
+        <v>45323</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" s="23">
+        <v>25000</v>
+      </c>
+      <c r="I13" s="15">
+        <v>31</v>
+      </c>
+      <c r="J13" s="14">
+        <v>31</v>
+      </c>
+      <c r="K13" s="14">
         <v>0</v>
       </c>
-      <c r="L11" s="14">
-        <f>Attandance!AK10</f>
+      <c r="L13" s="14">
         <v>0</v>
       </c>
-      <c r="M11" s="15"/>
-      <c r="N11" s="36">
+      <c r="M13" s="15"/>
+      <c r="N13" s="29">
         <f t="shared" si="0"/>
         <v>25000</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B14" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D14" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E14" s="22">
         <v>45536</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F14" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G14" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H12" s="30">
+      <c r="H14" s="23">
         <v>20000</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I14" s="15">
         <v>31</v>
       </c>
-      <c r="J12" s="14">
-        <f>Attandance!AM11</f>
+      <c r="J14" s="14">
         <v>31</v>
       </c>
-      <c r="K12" s="14">
-        <f>Attandance!AJ11</f>
+      <c r="K14" s="14">
         <v>0</v>
       </c>
-      <c r="L12" s="14">
-        <f>Attandance!AK11</f>
+      <c r="L14" s="14">
         <v>0</v>
       </c>
-      <c r="M12" s="15"/>
-      <c r="N12" s="36">
+      <c r="M14" s="15"/>
+      <c r="N14" s="29">
         <f t="shared" si="0"/>
         <v>20000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B15" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C15" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E15" s="22">
         <v>45566</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F15" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G15" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H15" s="23">
         <v>30000</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I15" s="15">
         <v>31</v>
       </c>
-      <c r="J13" s="14">
-        <f>Attandance!AM12</f>
-        <v>9</v>
-      </c>
-      <c r="K13" s="14">
-        <f>Attandance!AJ12</f>
-        <v>22</v>
-      </c>
-      <c r="L13" s="14">
-        <f>Attandance!AK12</f>
+      <c r="J15" s="14">
+        <v>31</v>
+      </c>
+      <c r="K15" s="14">
         <v>0</v>
       </c>
-      <c r="M13" s="15"/>
-      <c r="N13" s="36">
-        <f>(H13/30)*J13</f>
-        <v>9000</v>
+      <c r="L15" s="14">
+        <v>0</v>
+      </c>
+      <c r="M15" s="15"/>
+      <c r="N15" s="29">
+        <f>(H15/30)*J15</f>
+        <v>31000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="32" t="s">
+    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B16" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C16" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D16" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E16" s="26">
         <v>45559</v>
       </c>
-      <c r="F14" s="23" t="s">
+      <c r="F16" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G16" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="H14" s="34">
+      <c r="H16" s="27">
         <v>28000</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I16" s="18">
         <v>31</v>
       </c>
-      <c r="J14" s="22">
-        <f>Attandance!AM13</f>
+      <c r="J16" s="19">
         <v>31</v>
       </c>
-      <c r="K14" s="22">
-        <f>Attandance!AJ13</f>
+      <c r="K16" s="19">
         <v>0</v>
       </c>
-      <c r="L14" s="22">
-        <f>Attandance!AK13</f>
+      <c r="L16" s="19">
         <v>1</v>
       </c>
-      <c r="M14" s="35"/>
-      <c r="N14" s="50">
+      <c r="M16" s="28"/>
+      <c r="N16" s="43">
         <f t="shared" si="0"/>
         <v>28000</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:14" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="73" t="s">
+    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:14" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="74"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
-      <c r="J16" s="74"/>
-      <c r="K16" s="74"/>
-      <c r="L16" s="74"/>
-      <c r="M16" s="74"/>
-      <c r="N16" s="75"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="49"/>
+      <c r="M18" s="49"/>
+      <c r="N18" s="50"/>
     </row>
-    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="89" t="s">
+    <row r="19" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="76" t="s">
+      <c r="B20" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C20" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="76" t="s">
+      <c r="D20" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="55" t="s">
+      <c r="E20" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="55" t="s">
+      <c r="F20" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="G18" s="83" t="s">
+      <c r="G20" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="H18" s="83" t="s">
+      <c r="H20" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="I18" s="63" t="s">
+      <c r="I20" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="J18" s="63"/>
-      <c r="K18" s="63"/>
-      <c r="L18" s="63"/>
-      <c r="M18" s="86" t="s">
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="N18" s="58" t="s">
+      <c r="N20" s="51" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="90"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="84"/>
-      <c r="H19" s="84"/>
-      <c r="I19" s="77" t="s">
-        <v>39</v>
-      </c>
-      <c r="J19" s="79" t="s">
-        <v>40</v>
-      </c>
-      <c r="K19" s="81" t="s">
-        <v>41</v>
-      </c>
-      <c r="L19" s="81" t="s">
-        <v>42</v>
-      </c>
-      <c r="M19" s="87"/>
-      <c r="N19" s="59"/>
-    </row>
-    <row r="20" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="91"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="82"/>
-      <c r="L20" s="82"/>
-      <c r="M20" s="88"/>
-      <c r="N20" s="60"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="45">
-        <v>44475</v>
-      </c>
-      <c r="F21" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="G21" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="H21" s="48">
-        <v>60000</v>
-      </c>
-      <c r="I21" s="44">
-        <v>31</v>
-      </c>
-      <c r="J21" s="44">
-        <f>Attandance!AM19</f>
-        <v>29</v>
-      </c>
-      <c r="K21" s="44">
-        <f>Attandance!AJ19</f>
-        <v>1</v>
-      </c>
-      <c r="L21" s="44">
-        <f>Attandance!AK19</f>
-        <v>0</v>
-      </c>
-      <c r="M21" s="44"/>
-      <c r="N21" s="49">
-        <f>(H21/30)*J21</f>
-        <v>58000</v>
-      </c>
+      <c r="A21" s="59"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="J21" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="K21" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="L21" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="M21" s="67"/>
+      <c r="N21" s="52"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" s="16">
-        <v>45468</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G22" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="H22" s="19">
-        <v>24000</v>
-      </c>
-      <c r="I22" s="14">
-        <v>31</v>
-      </c>
-      <c r="J22" s="14">
-        <f>Attandance!AM20</f>
-        <v>31</v>
-      </c>
-      <c r="K22" s="14">
-        <f>Attandance!AJ20</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="14">
-        <f>Attandance!AK20</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="14"/>
-      <c r="N22" s="36">
-        <f>(H22/31)*J22</f>
-        <v>24000</v>
-      </c>
+    <row r="22" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="60"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="53"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="14" t="s">
+      <c r="A23" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="16">
-        <v>45505</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="H23" s="19">
-        <v>8000</v>
-      </c>
-      <c r="I23" s="14">
+      <c r="E23" s="38">
+        <v>44475</v>
+      </c>
+      <c r="F23" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23" s="41">
+        <v>60000</v>
+      </c>
+      <c r="I23" s="37">
         <v>31</v>
       </c>
-      <c r="J23" s="14">
-        <f>Attandance!AM21</f>
-        <v>31</v>
-      </c>
-      <c r="K23" s="14">
-        <f>Attandance!AJ21</f>
+      <c r="J23" s="37">
+        <v>29</v>
+      </c>
+      <c r="K23" s="37">
+        <v>1</v>
+      </c>
+      <c r="L23" s="37">
         <v>0</v>
       </c>
-      <c r="L23" s="14">
-        <f>Attandance!AK21</f>
-        <v>0</v>
-      </c>
-      <c r="M23" s="14"/>
-      <c r="N23" s="36">
-        <f>(H23/31)*J23</f>
-        <v>8000</v>
+      <c r="M23" s="37">
+        <v>25000</v>
+      </c>
+      <c r="N23" s="42">
+        <f>(H23/30)*J23+M23</f>
+        <v>83000</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
-        <v>26</v>
+      <c r="A24" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="16">
-        <v>44743</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="G24" s="28" t="s">
+      <c r="E24" s="22">
+        <v>45468</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H24" s="19">
-        <v>15000</v>
-      </c>
-      <c r="I24" s="14">
+      <c r="H24" s="23">
+        <v>24000</v>
+      </c>
+      <c r="I24" s="15">
         <v>31</v>
       </c>
-      <c r="J24" s="14">
-        <f>Attandance!AM22</f>
-        <v>10</v>
-      </c>
-      <c r="K24" s="14">
-        <f>Attandance!AJ22</f>
-        <v>21</v>
-      </c>
-      <c r="L24" s="14">
-        <f>Attandance!AK22</f>
+      <c r="J24" s="15">
+        <v>31</v>
+      </c>
+      <c r="K24" s="15">
         <v>0</v>
       </c>
-      <c r="M24" s="14"/>
-      <c r="N24" s="36">
-        <f>(H24/30)*J24</f>
-        <v>5000</v>
+      <c r="L24" s="15">
+        <v>0</v>
+      </c>
+      <c r="M24" s="15"/>
+      <c r="N24" s="73">
+        <f t="shared" ref="N24:N28" si="1">(H24/30)*J24+M24</f>
+        <v>24800</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
-        <v>28</v>
+      <c r="A25" s="24" t="s">
+        <v>24</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E25" s="16">
-        <v>44967</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G25" s="28" t="s">
+      <c r="E25" s="22">
+        <v>45505</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H25" s="19">
-        <v>15000</v>
-      </c>
-      <c r="I25" s="14">
+      <c r="H25" s="23">
+        <v>8000</v>
+      </c>
+      <c r="I25" s="15">
         <v>31</v>
       </c>
-      <c r="J25" s="14">
-        <f>Attandance!AM23</f>
+      <c r="J25" s="15">
         <v>31</v>
       </c>
-      <c r="K25" s="14">
-        <f>Attandance!AJ23</f>
+      <c r="K25" s="15">
         <v>0</v>
       </c>
-      <c r="L25" s="14">
-        <f>Attandance!AK23</f>
+      <c r="L25" s="15">
         <v>0</v>
       </c>
-      <c r="M25" s="14"/>
-      <c r="N25" s="36">
-        <f>(H25/31)*J25</f>
-        <v>15000</v>
+      <c r="M25" s="15"/>
+      <c r="N25" s="73">
+        <v>8000</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="22">
+        <v>44743</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" s="23">
+        <v>15000</v>
+      </c>
+      <c r="I26" s="15">
+        <v>31</v>
+      </c>
+      <c r="J26" s="15">
+        <v>10</v>
+      </c>
+      <c r="K26" s="15">
+        <v>21</v>
+      </c>
+      <c r="L26" s="15">
+        <v>0</v>
+      </c>
+      <c r="M26" s="15"/>
+      <c r="N26" s="73">
+        <f t="shared" si="1"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" s="22">
+        <v>44967</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27" s="23">
+        <v>15000</v>
+      </c>
+      <c r="I27" s="15">
+        <v>31</v>
+      </c>
+      <c r="J27" s="15">
+        <v>31</v>
+      </c>
+      <c r="K27" s="15">
+        <v>0</v>
+      </c>
+      <c r="L27" s="15">
+        <v>0</v>
+      </c>
+      <c r="M27" s="15"/>
+      <c r="N27" s="73">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B28" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D28" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E28" s="22">
         <v>45587</v>
       </c>
-      <c r="F26" s="27" t="s">
+      <c r="F28" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="G26" s="28" t="s">
+      <c r="G28" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H28" s="23">
         <v>15000</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I28" s="15">
         <v>31</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J28" s="15">
         <v>9</v>
       </c>
-      <c r="K26" s="14">
-        <f>Attandance!AJ24</f>
+      <c r="K28" s="15">
         <v>0</v>
       </c>
-      <c r="L26" s="14">
-        <f>Attandance!AK24</f>
+      <c r="L28" s="15">
         <v>0</v>
       </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="36">
-        <f>(H26/30)*J26</f>
+      <c r="M28" s="15"/>
+      <c r="N28" s="73">
+        <f t="shared" si="1"/>
         <v>4500</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="32" t="s">
+    <row r="29" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B29" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C29" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D29" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E29" s="26">
         <v>44959</v>
       </c>
-      <c r="F27" s="23" t="s">
+      <c r="F29" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="G27" s="24" t="s">
+      <c r="G29" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="H27" s="25">
+      <c r="H29" s="27">
         <v>15000</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I29" s="18">
         <v>31</v>
       </c>
-      <c r="J27" s="22">
-        <f>Attandance!AM25</f>
+      <c r="J29" s="18">
         <v>31</v>
       </c>
-      <c r="K27" s="22">
-        <f>Attandance!AJ25</f>
+      <c r="K29" s="18">
         <v>0</v>
       </c>
-      <c r="L27" s="22">
-        <f>Attandance!AK25</f>
+      <c r="L29" s="18">
         <v>0</v>
       </c>
-      <c r="M27" s="22"/>
-      <c r="N27" s="50">
-        <f>(H27/31)*J27</f>
+      <c r="M29" s="18"/>
+      <c r="N29" s="74">
         <v>15000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="34">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="N18:N20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="H18:H20"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="M18:M20"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="A16:N16"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="N5:N7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="M5:M7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="A18:N18"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="N20:N22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="F20:F22"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="H20:H22"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="M20:M22"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A5:A7"/>
   </mergeCells>
-  <conditionalFormatting sqref="B6:M6 B7:C10 M7:M13 D7:L14 C11:C13 F21:F27 D22:E26 K22:M27 D27:J27 G22:I26">
+  <conditionalFormatting sqref="B8:M8 B9:C12 M9:M15 D9:L16 C13:C15 F23:F29 K24:M29 D29:J29">
     <cfRule type="expression" dxfId="2" priority="9">
-      <formula>$C6=#REF!</formula>
+      <formula>$C8=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:C27">
+  <conditionalFormatting sqref="C23:C29">
     <cfRule type="expression" dxfId="1" priority="1">
-      <formula>$C21=#REF!</formula>
+      <formula>$C23=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D21:E21 G21:M21 B21:B26 J22:J26">
+  <conditionalFormatting sqref="G23:M23 B23:B28 D23:E28 G24:J28">
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>$C21=#REF!</formula>
+      <formula>$C23=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="78" fitToHeight="0" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="N13 N24 N26" formula="1"/>
+    <ignoredError sqref="N15" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>